--- a/Design/GrowthTree.xlsx
+++ b/Design/GrowthTree.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodes" sheetId="1" r:id="R591ae6cfc55d4ce9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effects" sheetId="2" r:id="R76d4c94fba8749fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="3" r:id="Rfcef83abb12c42f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodes" sheetId="1" r:id="Ra612e59466514400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effects" sheetId="2" r:id="R5628c944287d4825"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="3" r:id="Rbe71ecd22a9e4bd0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -531,10 +531,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G3" s="2" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>damage_4</x:v>
       </x:c>
       <x:c r="H3" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="6" t="n">
         <x:v>1470</x:v>
@@ -687,10 +687,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G7" s="2" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>experienceGradeChance_3</x:v>
       </x:c>
       <x:c r="H7" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="6" t="n">
         <x:v>-2100</x:v>
@@ -726,10 +726,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G8" s="2" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>time_2</x:v>
       </x:c>
       <x:c r="H8" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I8" s="6" t="n">
         <x:v>1050</x:v>
@@ -765,7 +765,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G9" s="2" t="str">
-        <x:v>speed_1</x:v>
+        <x:v>damage_1</x:v>
       </x:c>
       <x:c r="H9" s="5" t="n">
         <x:v>1</x:v>
@@ -804,7 +804,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G10" s="2" t="str">
-        <x:v>damage_1</x:v>
+        <x:v>speed_1</x:v>
       </x:c>
       <x:c r="H10" s="5" t="n">
         <x:v>1</x:v>
@@ -843,7 +843,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G11" s="2" t="str">
-        <x:v>population_1</x:v>
+        <x:v>magnet_1</x:v>
       </x:c>
       <x:c r="H11" s="5" t="n">
         <x:v>1</x:v>
@@ -882,7 +882,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G12" s="2" t="str">
-        <x:v>yield_1</x:v>
+        <x:v>population_1</x:v>
       </x:c>
       <x:c r="H12" s="5" t="n">
         <x:v>1</x:v>
@@ -921,7 +921,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G13" s="2" t="str">
-        <x:v>xp_1</x:v>
+        <x:v>extension_1</x:v>
       </x:c>
       <x:c r="H13" s="5" t="n">
         <x:v>1</x:v>
@@ -960,7 +960,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G14" s="2" t="str">
-        <x:v>population_1</x:v>
+        <x:v>xp_1</x:v>
       </x:c>
       <x:c r="H14" s="5" t="n">
         <x:v>1</x:v>
@@ -999,7 +999,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G15" s="2" t="str">
-        <x:v>time_1</x:v>
+        <x:v>damage_2</x:v>
       </x:c>
       <x:c r="H15" s="5" t="n">
         <x:v>1</x:v>
@@ -1038,7 +1038,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G16" s="2" t="str">
-        <x:v>extension_1</x:v>
+        <x:v>speed_2</x:v>
       </x:c>
       <x:c r="H16" s="5" t="n">
         <x:v>1</x:v>
@@ -1077,7 +1077,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G17" s="2" t="str">
-        <x:v>extension_1</x:v>
+        <x:v>time_1</x:v>
       </x:c>
       <x:c r="H17" s="5" t="n">
         <x:v>1</x:v>
@@ -1116,7 +1116,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G18" s="2" t="str">
-        <x:v>time_1</x:v>
+        <x:v>yield_1</x:v>
       </x:c>
       <x:c r="H18" s="5" t="n">
         <x:v>1</x:v>
@@ -1155,7 +1155,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G19" s="2" t="str">
-        <x:v>damage_1</x:v>
+        <x:v>damage_3</x:v>
       </x:c>
       <x:c r="H19" s="5" t="n">
         <x:v>1</x:v>
@@ -1194,7 +1194,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G20" s="2" t="str">
-        <x:v>damage_2</x:v>
+        <x:v>speed_3</x:v>
       </x:c>
       <x:c r="H20" s="5" t="n">
         <x:v>3</x:v>
@@ -1233,7 +1233,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G21" s="2" t="str">
-        <x:v>speed_2</x:v>
+        <x:v>respawn_1</x:v>
       </x:c>
       <x:c r="H21" s="5" t="n">
         <x:v>3</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G22" s="2" t="str">
-        <x:v>damage_3</x:v>
+        <x:v>xp_2</x:v>
       </x:c>
       <x:c r="H22" s="5" t="n">
         <x:v>3</x:v>
@@ -1311,7 +1311,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G23" s="2" t="str">
-        <x:v>yield_2</x:v>
+        <x:v>damage_4</x:v>
       </x:c>
       <x:c r="H23" s="5" t="n">
         <x:v>3</x:v>
@@ -1350,7 +1350,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G24" s="2" t="str">
-        <x:v>yield_2</x:v>
+        <x:v>speed_4</x:v>
       </x:c>
       <x:c r="H24" s="5" t="n">
         <x:v>3</x:v>
@@ -1389,7 +1389,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G25" s="2" t="str">
-        <x:v>population_2</x:v>
+        <x:v>time_2</x:v>
       </x:c>
       <x:c r="H25" s="5" t="n">
         <x:v>3</x:v>
@@ -1428,7 +1428,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G26" s="2" t="str">
-        <x:v>extension_2</x:v>
+        <x:v>yield_2</x:v>
       </x:c>
       <x:c r="H26" s="5" t="n">
         <x:v>3</x:v>
@@ -1467,7 +1467,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G27" s="2" t="str">
-        <x:v>xp_2</x:v>
+        <x:v>population_2</x:v>
       </x:c>
       <x:c r="H27" s="5" t="n">
         <x:v>3</x:v>
@@ -1506,7 +1506,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G28" s="2" t="str">
-        <x:v>damage_1</x:v>
+        <x:v>extension_2</x:v>
       </x:c>
       <x:c r="H28" s="5" t="n">
         <x:v>1</x:v>
@@ -1545,7 +1545,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G29" s="2" t="str">
-        <x:v>time_2</x:v>
+        <x:v>damage_5</x:v>
       </x:c>
       <x:c r="H29" s="5" t="n">
         <x:v>3</x:v>
@@ -1586,7 +1586,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G30" s="2" t="str">
-        <x:v>time_2</x:v>
+        <x:v>speed_5</x:v>
       </x:c>
       <x:c r="H30" s="5" t="n">
         <x:v>3</x:v>
@@ -1627,10 +1627,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G31" s="2" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>respawn_2</x:v>
       </x:c>
       <x:c r="H31" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I31" s="6" t="n">
         <x:v>-2310</x:v>
@@ -1666,7 +1666,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G32" s="2" t="str">
-        <x:v>speed_4</x:v>
+        <x:v>damage_6</x:v>
       </x:c>
       <x:c r="H32" s="5" t="n">
         <x:v>3</x:v>
@@ -1707,7 +1707,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G33" s="2" t="str">
-        <x:v>respawn_2</x:v>
+        <x:v>speed_6</x:v>
       </x:c>
       <x:c r="H33" s="5" t="n">
         <x:v>3</x:v>
@@ -1748,7 +1748,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G34" s="2" t="str">
-        <x:v>respawn_2</x:v>
+        <x:v>xp_3</x:v>
       </x:c>
       <x:c r="H34" s="5" t="n">
         <x:v>3</x:v>
@@ -1787,7 +1787,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G35" s="2" t="str">
-        <x:v>xp_3</x:v>
+        <x:v>damage_7</x:v>
       </x:c>
       <x:c r="H35" s="5" t="n">
         <x:v>3</x:v>
@@ -1828,7 +1828,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G36" s="2" t="str">
-        <x:v>damage_5</x:v>
+        <x:v>speed_7</x:v>
       </x:c>
       <x:c r="H36" s="5" t="n">
         <x:v>3</x:v>
@@ -1869,7 +1869,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G37" s="2" t="str">
-        <x:v>time_3</x:v>
+        <x:v>yield_3</x:v>
       </x:c>
       <x:c r="H37" s="5" t="n">
         <x:v>3</x:v>
@@ -1908,7 +1908,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G38" s="2" t="str">
-        <x:v>yield_3</x:v>
+        <x:v>respawn_3</x:v>
       </x:c>
       <x:c r="H38" s="5" t="n">
         <x:v>3</x:v>
@@ -1947,7 +1947,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="2" t="str">
-        <x:v>population_3</x:v>
+        <x:v>extension_3</x:v>
       </x:c>
       <x:c r="H39" s="5" t="n">
         <x:v>3</x:v>
@@ -1988,7 +1988,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G40" s="2" t="str">
-        <x:v>respawn_1</x:v>
+        <x:v>population_3</x:v>
       </x:c>
       <x:c r="H40" s="5" t="n">
         <x:v>3</x:v>
@@ -2027,7 +2027,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G41" s="2" t="str">
-        <x:v>respawn_1</x:v>
+        <x:v>time_3</x:v>
       </x:c>
       <x:c r="H41" s="5" t="n">
         <x:v>1</x:v>
@@ -2068,7 +2068,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G42" s="2" t="str">
-        <x:v>speed_6</x:v>
+        <x:v>damage_8</x:v>
       </x:c>
       <x:c r="H42" s="5" t="n">
         <x:v>3</x:v>
@@ -2107,7 +2107,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G43" s="2" t="str">
-        <x:v>respawn_3</x:v>
+        <x:v>speed_8</x:v>
       </x:c>
       <x:c r="H43" s="5" t="n">
         <x:v>3</x:v>
@@ -2146,7 +2146,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G44" s="2" t="str">
-        <x:v>damage_4</x:v>
+        <x:v>damage_9</x:v>
       </x:c>
       <x:c r="H44" s="5" t="n">
         <x:v>1</x:v>
@@ -2187,7 +2187,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G45" s="2" t="str">
-        <x:v>damage_7</x:v>
+        <x:v>speed_9</x:v>
       </x:c>
       <x:c r="H45" s="5" t="n">
         <x:v>3</x:v>
@@ -2228,7 +2228,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G46" s="2" t="str">
-        <x:v>speed_7</x:v>
+        <x:v>xp_4</x:v>
       </x:c>
       <x:c r="H46" s="5" t="n">
         <x:v>3</x:v>
@@ -2269,7 +2269,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G47" s="2" t="str">
-        <x:v>speed_8</x:v>
+        <x:v>damage_10</x:v>
       </x:c>
       <x:c r="H47" s="5" t="n">
         <x:v>3</x:v>
@@ -2310,7 +2310,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G48" s="2" t="str">
-        <x:v>speed_8</x:v>
+        <x:v>yield_4</x:v>
       </x:c>
       <x:c r="H48" s="5" t="n">
         <x:v>3</x:v>
@@ -2351,7 +2351,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G49" s="2" t="str">
-        <x:v>yield_4</x:v>
+        <x:v>respawn_4</x:v>
       </x:c>
       <x:c r="H49" s="5" t="n">
         <x:v>3</x:v>
@@ -2392,7 +2392,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G50" s="2" t="str">
-        <x:v>population_4</x:v>
+        <x:v>damage_11</x:v>
       </x:c>
       <x:c r="H50" s="5" t="n">
         <x:v>1</x:v>
@@ -2433,7 +2433,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G51" s="2" t="str">
-        <x:v>damage_6</x:v>
+        <x:v>damage_12</x:v>
       </x:c>
       <x:c r="H51" s="5" t="n">
         <x:v>3</x:v>
@@ -2472,7 +2472,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G52" s="2" t="str">
-        <x:v>speed_9</x:v>
+        <x:v>damage_13</x:v>
       </x:c>
       <x:c r="H52" s="5" t="n">
         <x:v>3</x:v>
@@ -2513,7 +2513,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G53" s="2" t="str">
-        <x:v>yield_1</x:v>
+        <x:v>yield_4</x:v>
       </x:c>
       <x:c r="H53" s="5" t="n">
         <x:v>1</x:v>
@@ -2552,7 +2552,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G54" s="2" t="str">
-        <x:v>xp_1</x:v>
+        <x:v>xp_4</x:v>
       </x:c>
       <x:c r="H54" s="5" t="n">
         <x:v>1</x:v>
@@ -2591,7 +2591,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G55" s="2" t="str">
-        <x:v>yield_3</x:v>
+        <x:v>silverDropChance_1</x:v>
       </x:c>
       <x:c r="H55" s="5" t="n">
         <x:v>2</x:v>
@@ -2630,7 +2630,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G56" s="2" t="str">
-        <x:v>xp_3</x:v>
+        <x:v>experienceGradeChance_1</x:v>
       </x:c>
       <x:c r="H56" s="5" t="n">
         <x:v>2</x:v>
@@ -2669,7 +2669,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G57" s="2" t="str">
-        <x:v>yield_5</x:v>
+        <x:v>silverDropChance_2</x:v>
       </x:c>
       <x:c r="H57" s="5" t="n">
         <x:v>3</x:v>
@@ -2708,7 +2708,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G58" s="2" t="str">
-        <x:v>xp_5</x:v>
+        <x:v>experienceGradeChance_2</x:v>
       </x:c>
       <x:c r="H58" s="5" t="n">
         <x:v>3</x:v>
@@ -2747,7 +2747,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G59" s="2" t="str">
-        <x:v>yield_2</x:v>
+        <x:v>yield_4</x:v>
       </x:c>
       <x:c r="H59" s="5" t="n">
         <x:v>1</x:v>
@@ -2786,7 +2786,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G60" s="2" t="str">
-        <x:v>damage_3</x:v>
+        <x:v>goldDropChance_1</x:v>
       </x:c>
       <x:c r="H60" s="5" t="n">
         <x:v>2</x:v>
@@ -2825,7 +2825,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G61" s="2" t="str">
-        <x:v>damage_4</x:v>
+        <x:v>goldDropChance_2</x:v>
       </x:c>
       <x:c r="H61" s="5" t="n">
         <x:v>3</x:v>
@@ -2864,7 +2864,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G62" s="2" t="str">
-        <x:v>speed_3</x:v>
+        <x:v>silverDropChance_2</x:v>
       </x:c>
       <x:c r="H62" s="5" t="n">
         <x:v>1</x:v>
@@ -2903,7 +2903,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G63" s="2" t="str">
-        <x:v>yield_3</x:v>
+        <x:v>emeraldDropChance_1</x:v>
       </x:c>
       <x:c r="H63" s="5" t="n">
         <x:v>2</x:v>
@@ -2942,7 +2942,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G64" s="2" t="str">
-        <x:v>damage_5</x:v>
+        <x:v>emeraldDropChance_2</x:v>
       </x:c>
       <x:c r="H64" s="5" t="n">
         <x:v>3</x:v>
@@ -2981,7 +2981,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G65" s="2" t="str">
-        <x:v>time_2</x:v>
+        <x:v>silverDropChance_3</x:v>
       </x:c>
       <x:c r="H65" s="5" t="n">
         <x:v>1</x:v>
@@ -3020,7 +3020,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G66" s="2" t="str">
-        <x:v>respawn_3</x:v>
+        <x:v>amethystDropChance_1</x:v>
       </x:c>
       <x:c r="H66" s="5" t="n">
         <x:v>2</x:v>
@@ -3059,7 +3059,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G67" s="2" t="str">
-        <x:v>speed_5</x:v>
+        <x:v>amethystDropChance_2</x:v>
       </x:c>
       <x:c r="H67" s="5" t="n">
         <x:v>3</x:v>
@@ -3098,7 +3098,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G68" s="2" t="str">
-        <x:v>population_1</x:v>
+        <x:v>time_3</x:v>
       </x:c>
       <x:c r="H68" s="5" t="n">
         <x:v>1</x:v>
@@ -3137,7 +3137,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G69" s="2" t="str">
-        <x:v>time_1</x:v>
+        <x:v>experienceGradeChance_2</x:v>
       </x:c>
       <x:c r="H69" s="5" t="n">
         <x:v>1</x:v>
@@ -3176,7 +3176,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G70" s="2" t="str">
-        <x:v>speed_1</x:v>
+        <x:v>damage_13</x:v>
       </x:c>
       <x:c r="H70" s="5" t="n">
         <x:v>1</x:v>
@@ -3215,10 +3215,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G71" s="2" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>speed_4</x:v>
       </x:c>
       <x:c r="H71" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I71" s="6" t="n">
         <x:v>2730</x:v>
@@ -3254,7 +3254,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G72" s="2" t="str">
-        <x:v>respawn_2</x:v>
+        <x:v>extension_2</x:v>
       </x:c>
       <x:c r="H72" s="5" t="n">
         <x:v>1</x:v>
@@ -3293,7 +3293,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G73" s="2" t="str">
-        <x:v>time_3</x:v>
+        <x:v>xp_4</x:v>
       </x:c>
       <x:c r="H73" s="5" t="n">
         <x:v>1</x:v>
@@ -3371,10 +3371,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G75" s="2" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>magic.projectile.damage</x:v>
       </x:c>
       <x:c r="H75" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I75" s="6" t="n">
         <x:v>420</x:v>
@@ -3410,7 +3410,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G76" s="2" t="str">
-        <x:v>magic.projectile.damage</x:v>
+        <x:v>magic.projectile.speed</x:v>
       </x:c>
       <x:c r="H76" s="5" t="n">
         <x:v>1</x:v>
@@ -3449,7 +3449,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G77" s="2" t="str">
-        <x:v>magic.projectile.damage</x:v>
+        <x:v>magic.projectile.count</x:v>
       </x:c>
       <x:c r="H77" s="5" t="n">
         <x:v>1</x:v>
@@ -3488,7 +3488,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G78" s="2" t="str">
-        <x:v>magic.projectile.damage</x:v>
+        <x:v>magic.projectile.pierce</x:v>
       </x:c>
       <x:c r="H78" s="5" t="n">
         <x:v>1</x:v>
@@ -3568,10 +3568,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G80" s="2" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>magic.flame.damage</x:v>
       </x:c>
       <x:c r="H80" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I80" s="6" t="n">
         <x:v>420</x:v>
@@ -3607,7 +3607,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G81" s="2" t="str">
-        <x:v>magic.flame.damage</x:v>
+        <x:v>magic.flame.speed</x:v>
       </x:c>
       <x:c r="H81" s="5" t="n">
         <x:v>1</x:v>
@@ -3646,7 +3646,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G82" s="2" t="str">
-        <x:v>magic.flame.damage</x:v>
+        <x:v>magic.flame.range</x:v>
       </x:c>
       <x:c r="H82" s="5" t="n">
         <x:v>1</x:v>
@@ -3685,7 +3685,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G83" s="2" t="str">
-        <x:v>magic.flame.damage</x:v>
+        <x:v>magic.flame.width</x:v>
       </x:c>
       <x:c r="H83" s="5" t="n">
         <x:v>1</x:v>
@@ -3765,10 +3765,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G85" s="2" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>magic.lightning.damage</x:v>
       </x:c>
       <x:c r="H85" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I85" s="6" t="n">
         <x:v>420</x:v>
@@ -3804,7 +3804,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G86" s="2" t="str">
-        <x:v>magic.lightning.damage</x:v>
+        <x:v>magic.lightning.speed</x:v>
       </x:c>
       <x:c r="H86" s="5" t="n">
         <x:v>1</x:v>
@@ -3843,7 +3843,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G87" s="2" t="str">
-        <x:v>magic.lightning.damage</x:v>
+        <x:v>magic.lightning.jumps</x:v>
       </x:c>
       <x:c r="H87" s="5" t="n">
         <x:v>1</x:v>
@@ -3882,7 +3882,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G88" s="2" t="str">
-        <x:v>magic.lightning.damage</x:v>
+        <x:v>magic.lightning.range</x:v>
       </x:c>
       <x:c r="H88" s="5" t="n">
         <x:v>1</x:v>
@@ -3962,10 +3962,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G90" s="2" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>magic.frost.damage</x:v>
       </x:c>
       <x:c r="H90" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I90" s="6" t="n">
         <x:v>420</x:v>
@@ -4001,7 +4001,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G91" s="2" t="str">
-        <x:v>magic.frost.damage</x:v>
+        <x:v>magic.frost.speed</x:v>
       </x:c>
       <x:c r="H91" s="5" t="n">
         <x:v>1</x:v>
@@ -4040,7 +4040,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G92" s="2" t="str">
-        <x:v>magic.frost.damage</x:v>
+        <x:v>magic.frost.count</x:v>
       </x:c>
       <x:c r="H92" s="5" t="n">
         <x:v>1</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G93" s="2" t="str">
-        <x:v>magic.frost.damage</x:v>
+        <x:v>magic.frost.orbitSpeed</x:v>
       </x:c>
       <x:c r="H93" s="5" t="n">
         <x:v>1</x:v>
@@ -4120,7 +4120,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G94" s="2" t="str">
-        <x:v>magic.frost.damage</x:v>
+        <x:v>magic.frost.range</x:v>
       </x:c>
       <x:c r="H94" s="5" t="n">
         <x:v>1</x:v>
@@ -4161,7 +4161,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G95" s="2" t="str">
-        <x:v>magic.frost.damage</x:v>
+        <x:v>magic.frost.size</x:v>
       </x:c>
       <x:c r="H95" s="5" t="n">
         <x:v>1</x:v>
@@ -4200,7 +4200,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G96" s="2" t="str">
-        <x:v>magic.frost.damage</x:v>
+        <x:v>magic.frost.chill</x:v>
       </x:c>
       <x:c r="H96" s="5" t="n">
         <x:v>1</x:v>
@@ -4241,7 +4241,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G97" t="str">
-        <x:v>xp_1</x:v>
+        <x:v>magnet_1</x:v>
       </x:c>
       <x:c r="H97" t="n">
         <x:v>1</x:v>
@@ -4563,7 +4563,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G105" t="str">
-        <x:v>population_1</x:v>
+        <x:v>movement_1</x:v>
       </x:c>
       <x:c r="H105" t="n">
         <x:v>1</x:v>
@@ -4840,7 +4840,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G112" t="str">
-        <x:v>population_1</x:v>
+        <x:v>movement_1</x:v>
       </x:c>
       <x:c r="H112" t="n">
         <x:v>1</x:v>
@@ -4998,7 +4998,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G116" t="str">
-        <x:v>magnet_1</x:v>
+        <x:v>population_4</x:v>
       </x:c>
       <x:c r="H116" t="n">
         <x:v>1</x:v>
@@ -5115,7 +5115,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G119" t="str">
-        <x:v>magic.projectile.beamUnlock</x:v>
+        <x:v>magic.projectile.beamPower</x:v>
       </x:c>
       <x:c r="H119" t="n">
         <x:v>1</x:v>
@@ -5154,7 +5154,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G120" t="str">
-        <x:v>magic.projectile.beamUnlock</x:v>
+        <x:v>magic.projectile.beamWidth</x:v>
       </x:c>
       <x:c r="H120" t="n">
         <x:v>1</x:v>
@@ -5193,7 +5193,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G121" t="str">
-        <x:v>magic.projectile.beamUnlock</x:v>
+        <x:v>magic.projectile.beamCount</x:v>
       </x:c>
       <x:c r="H121" t="n">
         <x:v>1</x:v>
@@ -5312,7 +5312,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G124" t="str">
-        <x:v>magic.projectile.satelliteUnlock</x:v>
+        <x:v>magic.projectile.satellitePower</x:v>
       </x:c>
       <x:c r="H124" t="n">
         <x:v>1</x:v>
@@ -5351,7 +5351,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G125" t="str">
-        <x:v>magic.projectile.satelliteUnlock</x:v>
+        <x:v>magic.projectile.satelliteCount</x:v>
       </x:c>
       <x:c r="H125" t="n">
         <x:v>1</x:v>
@@ -5390,7 +5390,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G126" t="str">
-        <x:v>magic.projectile.satelliteUnlock</x:v>
+        <x:v>magic.projectile.satelliteRate</x:v>
       </x:c>
       <x:c r="H126" t="n">
         <x:v>1</x:v>
@@ -5431,7 +5431,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G127" t="str">
-        <x:v>magic.projectile.damage</x:v>
+        <x:v>magic.projectile.homing</x:v>
       </x:c>
       <x:c r="H127" t="n">
         <x:v>1</x:v>
@@ -5550,7 +5550,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G130" t="str">
-        <x:v>magic.flame.firefieldUnlock</x:v>
+        <x:v>magic.flame.firefieldPower</x:v>
       </x:c>
       <x:c r="H130" t="n">
         <x:v>1</x:v>
@@ -5589,7 +5589,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G131" t="str">
-        <x:v>magic.flame.firefieldUnlock</x:v>
+        <x:v>magic.flame.firefieldRange</x:v>
       </x:c>
       <x:c r="H131" t="n">
         <x:v>1</x:v>
@@ -5628,7 +5628,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G132" t="str">
-        <x:v>magic.flame.firefieldUnlock</x:v>
+        <x:v>magic.flame.firefieldCount</x:v>
       </x:c>
       <x:c r="H132" t="n">
         <x:v>1</x:v>
@@ -5747,7 +5747,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G135" t="str">
-        <x:v>magic.flame.meteorUnlock</x:v>
+        <x:v>magic.flame.meteorPower</x:v>
       </x:c>
       <x:c r="H135" t="n">
         <x:v>1</x:v>
@@ -5786,7 +5786,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G136" t="str">
-        <x:v>magic.flame.meteorUnlock</x:v>
+        <x:v>magic.flame.meteorRange</x:v>
       </x:c>
       <x:c r="H136" t="n">
         <x:v>1</x:v>
@@ -5825,7 +5825,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G137" t="str">
-        <x:v>magic.flame.meteorUnlock</x:v>
+        <x:v>magic.flame.meteorCount</x:v>
       </x:c>
       <x:c r="H137" t="n">
         <x:v>1</x:v>
@@ -5866,7 +5866,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G138" t="str">
-        <x:v>magic.flame.damage</x:v>
+        <x:v>magic.flame.burn</x:v>
       </x:c>
       <x:c r="H138" t="n">
         <x:v>1</x:v>
@@ -5985,7 +5985,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G141" t="str">
-        <x:v>magic.lightning.orbUnlock</x:v>
+        <x:v>magic.lightning.orbPower</x:v>
       </x:c>
       <x:c r="H141" t="n">
         <x:v>1</x:v>
@@ -6024,7 +6024,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G142" t="str">
-        <x:v>magic.lightning.orbUnlock</x:v>
+        <x:v>magic.lightning.orbRange</x:v>
       </x:c>
       <x:c r="H142" t="n">
         <x:v>1</x:v>
@@ -6063,7 +6063,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G143" t="str">
-        <x:v>magic.lightning.orbUnlock</x:v>
+        <x:v>magic.lightning.orbCount</x:v>
       </x:c>
       <x:c r="H143" t="n">
         <x:v>1</x:v>
@@ -6182,7 +6182,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G146" t="str">
-        <x:v>magic.lightning.thunderUnlock</x:v>
+        <x:v>magic.lightning.thunderPower</x:v>
       </x:c>
       <x:c r="H146" t="n">
         <x:v>1</x:v>
@@ -6221,7 +6221,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G147" t="str">
-        <x:v>magic.lightning.thunderUnlock</x:v>
+        <x:v>magic.lightning.thunderRange</x:v>
       </x:c>
       <x:c r="H147" t="n">
         <x:v>1</x:v>
@@ -6260,7 +6260,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G148" t="str">
-        <x:v>magic.lightning.thunderUnlock</x:v>
+        <x:v>magic.lightning.thunderCount</x:v>
       </x:c>
       <x:c r="H148" t="n">
         <x:v>1</x:v>
@@ -6301,7 +6301,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G149" t="str">
-        <x:v>magic.lightning.damage</x:v>
+        <x:v>magic.lightning.echo</x:v>
       </x:c>
       <x:c r="H149" t="n">
         <x:v>1</x:v>
@@ -6420,7 +6420,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G152" t="str">
-        <x:v>magic.frost.blizzardUnlock</x:v>
+        <x:v>magic.frost.blizzardPower</x:v>
       </x:c>
       <x:c r="H152" t="n">
         <x:v>1</x:v>
@@ -6459,7 +6459,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G153" t="str">
-        <x:v>magic.frost.blizzardUnlock</x:v>
+        <x:v>magic.frost.blizzardRange</x:v>
       </x:c>
       <x:c r="H153" t="n">
         <x:v>1</x:v>
@@ -6498,7 +6498,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G154" t="str">
-        <x:v>magic.frost.blizzardUnlock</x:v>
+        <x:v>magic.frost.blizzardCount</x:v>
       </x:c>
       <x:c r="H154" t="n">
         <x:v>1</x:v>
@@ -6617,7 +6617,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G157" t="str">
-        <x:v>magic.frost.shatterUnlock</x:v>
+        <x:v>magic.frost.shatterPower</x:v>
       </x:c>
       <x:c r="H157" t="n">
         <x:v>1</x:v>
@@ -6656,7 +6656,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G158" t="str">
-        <x:v>magic.frost.shatterUnlock</x:v>
+        <x:v>magic.frost.shatterRange</x:v>
       </x:c>
       <x:c r="H158" t="n">
         <x:v>1</x:v>
@@ -6695,7 +6695,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G159" t="str">
-        <x:v>magic.frost.shatterUnlock</x:v>
+        <x:v>magic.frost.shatterShards</x:v>
       </x:c>
       <x:c r="H159" t="n">
         <x:v>1</x:v>
@@ -6736,7 +6736,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G160" t="str">
-        <x:v>magic.frost.damage</x:v>
+        <x:v>magic.frost.freezeDuration</x:v>
       </x:c>
       <x:c r="H160" t="n">
         <x:v>1</x:v>
@@ -6784,7 +6784,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4eeb06a9dde94dbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b5b79c5cb614af7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9358,7 +9358,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc14165051365415b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5935dec3bc743c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
